--- a/inst/extdata/Livestock_coefs.xlsx
+++ b/inst/extdata/Livestock_coefs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0dd767e02e6ada6c/Documents/GitHub/afsetools/inst/extdata/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\53272530E\OneDrive\Documents\GitHub\afsetools\inst\extdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFB44491-5F41-400E-B738-6F3D9AA43E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F41359A3-F318-4CEC-9432-77843AA152DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4900" yWindow="8800" windowWidth="7850" windowHeight="11550" xr2:uid="{6EFA3176-6F2D-49CC-BD73-7F1E09DA449D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{6EFA3176-6F2D-49CC-BD73-7F1E09DA449D}"/>
   </bookViews>
   <sheets>
     <sheet name="max_intake" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,6 @@
   <externalReferences>
     <externalReference r:id="rId2"/>
     <externalReference r:id="rId3"/>
-    <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
     <definedName name="fish">[1]HS6_list!$E$6:$L$288</definedName>
@@ -26,7 +25,7 @@
     <definedName name="hs4list">#REF!</definedName>
     <definedName name="hs6list">#REF!</definedName>
     <definedName name="list_plant">#REF!</definedName>
-    <definedName name="UNECE">'[3]net increment_UNECE'!$B$4:$D$50</definedName>
+    <definedName name="UNECE">'[2]net increment_UNECE'!$B$4:$D$50</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,10 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="19">
-  <si>
-    <t>Grassland</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="22">
   <si>
     <t>Aquaculture</t>
   </si>
@@ -106,6 +102,18 @@
   </si>
   <si>
     <t>Livestock_cat</t>
+  </si>
+  <si>
+    <t>var</t>
+  </si>
+  <si>
+    <t>Cat_feed</t>
+  </si>
+  <si>
+    <t>Grass</t>
+  </si>
+  <si>
+    <t>var_value</t>
   </si>
 </sst>
 </file>
@@ -5876,111 +5884,6 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Provincial"/>
-      <sheetName val="Prod_N"/>
-      <sheetName val="Prod_LHA"/>
-      <sheetName val="Item_Prod_LHA"/>
-      <sheetName val="Extensivo_trad"/>
-      <sheetName val="Feed_tot"/>
-      <sheetName val="FishIntake_aquacult"/>
-      <sheetName val="Live_to_products"/>
-      <sheetName val="Efficiency_LHA"/>
-      <sheetName val="Excretion_RGR"/>
-      <sheetName val="Excretion_animal"/>
-      <sheetName val="Manure_destinies"/>
-      <sheetName val="Manure_losses"/>
-      <sheetName val="LW_Soto"/>
-      <sheetName val="Invent"/>
-      <sheetName val="Production_FAO"/>
-      <sheetName val="Stock_FAO"/>
-      <sheetName val="Stock_LW"/>
-      <sheetName val="Stock_number"/>
-      <sheetName val="LW"/>
-      <sheetName val="Cattle_LW"/>
-      <sheetName val="LW_animal"/>
-      <sheetName val="Prod_year"/>
-      <sheetName val="Prod_year_N"/>
-      <sheetName val="Manure_inorganic_N"/>
-      <sheetName val="NH3_EFs_EMEP"/>
-      <sheetName val="Manure_inorganic_N_refs"/>
-      <sheetName val="Names_NIR_Species"/>
-      <sheetName val="Names_all"/>
-      <sheetName val="Names_manure_dest"/>
-      <sheetName val="Names_categoria_Species"/>
-      <sheetName val="Names_Livestock_cat"/>
-      <sheetName val="Names_live"/>
-      <sheetName val="LiveWeight"/>
-      <sheetName val="Poultry_rabbits"/>
-      <sheetName val="Grazing_EFs"/>
-      <sheetName val="Animals_FCR"/>
-      <sheetName val="Grazing_shares"/>
-      <sheetName val="Grass_yields"/>
-      <sheetName val="Diet_composition"/>
-      <sheetName val="Energy_destinies"/>
-      <sheetName val="Manure_CH4_to_N"/>
-      <sheetName val="Destinies_cats"/>
-      <sheetName val="Systems_cats"/>
-      <sheetName val="subcat_k"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-      <sheetData sheetId="23"/>
-      <sheetData sheetId="24"/>
-      <sheetData sheetId="25"/>
-      <sheetData sheetId="26"/>
-      <sheetData sheetId="27"/>
-      <sheetData sheetId="28"/>
-      <sheetData sheetId="29"/>
-      <sheetData sheetId="30"/>
-      <sheetData sheetId="31"/>
-      <sheetData sheetId="32"/>
-      <sheetData sheetId="33"/>
-      <sheetData sheetId="34"/>
-      <sheetData sheetId="35"/>
-      <sheetData sheetId="36"/>
-      <sheetData sheetId="37"/>
-      <sheetData sheetId="38"/>
-      <sheetData sheetId="39"/>
-      <sheetData sheetId="40"/>
-      <sheetData sheetId="41"/>
-      <sheetData sheetId="42"/>
-      <sheetData sheetId="43"/>
-      <sheetData sheetId="44"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -6782,329 +6685,416 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E40C1CFF-91A3-42AF-B420-3A43F4F225F5}">
-  <dimension ref="A1:C29"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.1796875" customWidth="1"/>
-    <col min="3" max="3" width="8.7265625" style="1"/>
+    <col min="1" max="2" width="14.19921875" customWidth="1"/>
+    <col min="4" max="4" width="8.73046875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" t="s">
         <v>18</v>
       </c>
-      <c r="B1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
         <v>16</v>
       </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="1">
+        <v>0.05</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="1">
-        <v>0.05</v>
+      <c r="D3" s="1">
+        <v>0.1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="1">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
         <v>13</v>
       </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="1">
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>10</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" t="s">
+        <v>20</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" s="1">
         <v>0.1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="1">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="1">
-        <v>0.01</v>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" s="1">
+        <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="1">
-        <v>0.01</v>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>2</v>
+      </c>
+      <c r="B27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="1">
-        <v>0.4</v>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="1">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>2</v>
-      </c>
-      <c r="B14" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>1</v>
-      </c>
-      <c r="B15" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>0</v>
-      </c>
-      <c r="C16" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" t="s">
-        <v>0</v>
-      </c>
-      <c r="C17" s="1">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" t="s">
-        <v>0</v>
-      </c>
-      <c r="C18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>11</v>
-      </c>
-      <c r="B19" t="s">
-        <v>0</v>
-      </c>
-      <c r="C19" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>10</v>
-      </c>
-      <c r="B20" t="s">
-        <v>0</v>
-      </c>
-      <c r="C20" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" t="s">
-        <v>0</v>
-      </c>
-      <c r="C21" s="1">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>8</v>
-      </c>
-      <c r="B22" t="s">
-        <v>0</v>
-      </c>
-      <c r="C22" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>7</v>
-      </c>
-      <c r="B23" t="s">
-        <v>0</v>
-      </c>
-      <c r="C23" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>6</v>
-      </c>
-      <c r="B24" t="s">
-        <v>0</v>
-      </c>
-      <c r="C24" s="1">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" t="s">
-        <v>0</v>
-      </c>
-      <c r="C25" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" t="s">
-        <v>0</v>
-      </c>
-      <c r="C26" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>3</v>
-      </c>
-      <c r="B27" t="s">
-        <v>0</v>
-      </c>
-      <c r="C27" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>2</v>
-      </c>
-      <c r="B28" t="s">
-        <v>0</v>
-      </c>
-      <c r="C28" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>1</v>
-      </c>
       <c r="B29" t="s">
-        <v>0</v>
-      </c>
-      <c r="C29" s="1">
+        <v>19</v>
+      </c>
+      <c r="C29" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="1">
         <v>0</v>
       </c>
     </row>
